--- a/artfynd/A 58661-2021 artfynd.xlsx
+++ b/artfynd/A 58661-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58661-2021 artfynd.xlsx
+++ b/artfynd/A 58661-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,220 +907,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>112605313</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5160</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bygdeträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>770631</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7155823</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2022-11-06</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2022-11-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>112605312</v>
-      </c>
-      <c r="B5" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Bygdeträsk, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>770690</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7155800</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-11-06</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-11-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
